--- a/CRONOGRAMA.xlsx
+++ b/CRONOGRAMA.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AULAS\COMPONENTES\PTCC\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B681B909-E51C-423D-8A7E-0A031C2466BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A03428C-6A59-4E5B-ABA9-FA5814DC0F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{F214736B-ADF1-40C6-8B42-E4590974EE23}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>CRONOGRAMA</t>
   </si>
@@ -57,6 +58,54 @@
   </si>
   <si>
     <t>CHECK</t>
+  </si>
+  <si>
+    <t>Gabriel da Silva Rodrigues</t>
+  </si>
+  <si>
+    <t>Gabriela Carravieri Sena</t>
+  </si>
+  <si>
+    <t>Maria Eduarda dos Santos Nascimento</t>
+  </si>
+  <si>
+    <t>Maria Madalena Ferreira da Silva</t>
+  </si>
+  <si>
+    <t>Mariana Fernandes da Silva</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Bertojna Santiago</t>
+  </si>
+  <si>
+    <t>Introdução e dificuldades</t>
+  </si>
+  <si>
+    <t>Pesquisa de mercado</t>
+  </si>
+  <si>
+    <t>Proposta</t>
+  </si>
+  <si>
+    <t>Objetivos e solução</t>
+  </si>
+  <si>
+    <t>Problema de pesquisa e Conclusão</t>
+  </si>
+  <si>
+    <t>Check's</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não feito</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hipóteses </t>
   </si>
 </sst>
 </file>
@@ -80,15 +129,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -148,30 +209,257 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -182,6 +470,16 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C254C37F-36F2-41B1-B6CF-0FD8AB39E09F}" name="Tabela1" displayName="Tabela1" ref="F3:F6" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+  <autoFilter ref="F3:F6" xr:uid="{C254C37F-36F2-41B1-B6CF-0FD8AB39E09F}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{6ADD6C70-281E-4079-B999-43DB19E9B29F}" name="Check's" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -501,12 +799,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9CBCC9-A42A-40AF-B12F-FCF643C41317}">
-  <dimension ref="B2:F8"/>
+  <dimension ref="B2:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
@@ -536,45 +836,177 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9">
+        <v>46098</v>
+      </c>
+      <c r="E4" s="9">
+        <v>46099</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="9">
+        <v>46096</v>
+      </c>
+      <c r="E5" s="9">
+        <v>46099</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9">
+        <v>46092</v>
+      </c>
+      <c r="E6" s="9">
+        <v>46099</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46093</v>
+      </c>
+      <c r="E7" s="9">
+        <v>46099</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="9">
+        <v>46094</v>
+      </c>
+      <c r="E8" s="9">
+        <v>46099</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="9">
+        <v>46094</v>
+      </c>
+      <c r="E9" s="9">
+        <v>46099</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
+  <conditionalFormatting sqref="F4:F9">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"Não feito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"Fazendo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Está fazendo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"Não fez"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+      <formula>"Feito"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A4E2182C-2DE0-40D1-86B1-6DED8B18B47E}">
+          <x14:formula1>
+            <xm:f>Planilha2!$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>F4:F9</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4287326-6093-4B87-BB48-4EF06A07607F}">
+  <dimension ref="F3:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>